--- a/business_forms/050_seller_s_product_evaluation_questionnaire--business_forms.xlsx
+++ b/business_forms/050_seller_s_product_evaluation_questionnaire--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'excellent'}</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Excellent'}</t>
+          <t>Excellent</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'bad'}</t>
+          <t>bad</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Bad'}</t>
+          <t>Bad</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_bad'}</t>
+          <t>very_bad</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Bad'}</t>
+          <t>Very Bad</t>
         </is>
       </c>
     </row>
